--- a/recommendation_forms/023_property_manager_recommendation_form--recommendation_forms.xlsx
+++ b/recommendation_forms/023_property_manager_recommendation_form--recommendation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'rental'}</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Rental'}</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'owner_occupied'}</t>
+          <t>owner_occupied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Owner Occupied'}</t>
+          <t>Owner Occupied</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'single_family_home'}</t>
+          <t>single_family_home</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Single Family Home'}</t>
+          <t>Single Family Home</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'duplex'}</t>
+          <t>duplex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Duplex'}</t>
+          <t>Duplex</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'multi-unit'}</t>
+          <t>multi-unit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Multi-Unit'}</t>
+          <t>Multi-Unit</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
